--- a/jogos_2024-09-16.xlsx
+++ b/jogos_2024-09-16.xlsx
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>2.67</v>
       </c>
       <c r="M9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.6</v>
       </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X9" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="Y9" t="n">
         <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AB9" t="n">
         <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['9', '34', '53']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.16</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45551.45833333334</v>
@@ -1665,33 +1665,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
         <v>2.2</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.75</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.99</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
         <v>1.25</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['9', '34', '53']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45551.45833333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>3.11</v>
+        <v>5.14</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.25</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC11" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['3', '62']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
         <v>1.71</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45551.47916666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>5.14</v>
+        <v>3.11</v>
       </c>
       <c r="O12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['3', '62']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.36</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
         <v>1.71</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45551.47916666666</v>
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45551.54166666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.9</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.6</v>
-      </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>5.25</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.38</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.94</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45551.54166666666</v>
@@ -2707,16 +2707,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,43 +2733,43 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="M18" t="n">
         <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
         <v>1.9</v>
@@ -2778,10 +2778,10 @@
         <v>1.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
         <v>1.83</v>
@@ -2791,22 +2791,22 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AJ18" t="n">
         <v>1.5</v>
@@ -3223,81 +3223,81 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC22" t="n">
         <v>1.5</v>
@@ -3307,25 +3307,25 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['27', '63']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45551.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>17</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.73</v>
-      </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.81</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['22', '62']</t>
+          <t>['29', '82']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '26', '50']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>7.5</v>
+        <v>1.87</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AJ23" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45551.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
         <v>3.3</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="Z24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>['17', '41']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
       <c r="AG24" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45551.58333333334</v>
@@ -3600,35 +3600,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45551.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,16 +3739,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.4</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>4.22</v>
+        <v>4.55</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['50', '90+8']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
         <v>2.05</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45551.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.7</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="O28" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>4.55</v>
+        <v>6.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.43</v>
+        <v>1.92</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>['22', '62']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4126,81 +4126,81 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
+      <c r="Z29" t="n">
         <v>1.8</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA29" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
         <v>1.8</v>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['29', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['13', '26', '50']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4245,35 +4245,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>2.79</v>
+        <v>4.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.74</v>
+        <v>2.38</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AI30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>3.74</v>
+        <v>1.9</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.4</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['4', '43', '84']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="N32" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O32" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="U32" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>5.15</v>
+        <v>6.35</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['10', '31', '41', '62', '90+1']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['27', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.2</v>
       </c>
-      <c r="AH32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X33" t="n">
         <v>3.28</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.3</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['17', '41']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AI33" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4761,119 +4761,119 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M34" t="n">
-        <v>7</v>
-      </c>
-      <c r="N34" t="n">
-        <v>11</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X34" t="n">
         <v>3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="Y34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.2</v>
       </c>
-      <c r="S34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X34" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['10', '31', '41', '62', '90+1']</t>
+          <t>['4', '43', '84']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.95</v>
+        <v>1.73</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AJ34" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45551.58333333334</v>
@@ -4890,32 +4890,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="N35" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>['50', '90+8']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45551.58333333334</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S36" t="n">
         <v>3.5</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.85</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.81</v>
+        <v>2.25</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.18</v>
+        <v>2.35</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45551.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,19 +5416,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="N39" t="n">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="O39" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.79</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>3.56</v>
+        <v>3.83</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '62']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45551.625</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="M40" t="n">
-        <v>4.17</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="P40" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.9</v>
+        <v>4.64</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>3.85</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U40" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="X40" t="n">
-        <v>5.01</v>
+        <v>2.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['6', '17', '22', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '60']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45551.625</v>
@@ -5664,29 +5664,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.19</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y41" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q41" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5763,20 +5763,20 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45551.625</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="N42" t="n">
-        <v>3.6</v>
+        <v>3.19</v>
       </c>
       <c r="O42" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.63</v>
       </c>
       <c r="R42" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.25</v>
       </c>
-      <c r="U42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X42" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB42" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['30', '51', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['44', '60', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45551.625</v>
@@ -5922,32 +5922,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>4.17</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="P43" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="R43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U43" t="n">
         <v>1.57</v>
       </c>
-      <c r="S43" t="n">
+      <c r="V43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z43" t="n">
         <v>2.25</v>
       </c>
-      <c r="T43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X43" t="n">
+      <c r="AA43" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AB43" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
+          <t>['6', '17', '22', '85']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
       <c r="AG43" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.36</v>
+        <v>2.41</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45551.625</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.54</v>
+        <v>3.93</v>
       </c>
       <c r="N44" t="n">
-        <v>1.78</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
         <v>4</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['30', '51', '69']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['44', '60', '90']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>1.25</v>
       </c>
-      <c r="X44" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z44" t="n">
+      <c r="AH44" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA44" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['50', '62']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI44" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45551.625</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N45" t="n">
-        <v>2.81</v>
+        <v>3.56</v>
       </c>
       <c r="O45" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>4.79</v>
       </c>
       <c r="R45" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.33</v>
       </c>
-      <c r="S45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC45" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['12', '29', '51']</t>
-        </is>
-      </c>
       <c r="AG45" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45551.625</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,87 +6319,87 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>2</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="O46" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.64</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S46" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="T46" t="n">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="U46" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X46" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['30', '60']</t>
+          <t>['12', '29', '51']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45551.625</v>
@@ -6825,35 +6825,35 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,28 +6861,28 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S50" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T50" t="n">
         <v>3.75</v>
@@ -6891,53 +6891,53 @@
         <v>1.25</v>
       </c>
       <c r="V50" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W50" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Z50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>['20', '84']</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
         <v>1.44</v>
       </c>
-      <c r="AA50" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45551.65625</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.73</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.49</v>
+        <v>5.75</v>
       </c>
       <c r="O51" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="P51" t="n">
         <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="R51" t="n">
         <v>1.4</v>
@@ -7020,53 +7020,53 @@
         <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X51" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD51" t="n">
-        <v>2</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['42', '45', '59']</t>
+          <t>['49', '90+3']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AG51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45551.65625</v>
@@ -7212,35 +7212,35 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,28 +7248,28 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S53" t="n">
         <v>2.25</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.38</v>
       </c>
       <c r="T53" t="n">
         <v>3.75</v>
@@ -7278,53 +7278,53 @@
         <v>1.25</v>
       </c>
       <c r="V53" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X53" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AA53" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['20', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45551.65625</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,22 +7480,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -7506,22 +7506,22 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.57</v>
+        <v>2.73</v>
       </c>
       <c r="M55" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O55" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.1</v>
       </c>
       <c r="P55" t="n">
         <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
         <v>1.4</v>
@@ -7536,53 +7536,53 @@
         <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X55" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y55" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD55" t="n">
         <v>2</v>
       </c>
-      <c r="Z55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['49', '90+3']</t>
+          <t>['42', '45', '59']</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.06</v>
+        <v>1.4</v>
       </c>
       <c r="AI55" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45551.65625</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7624,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="M56" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="N56" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="O56" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P56" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q56" t="n">
         <v>4.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="T56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>['50', '66', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ56" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['22', '52', '59']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45551.66666666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7753,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="N57" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="O57" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="P57" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q57" t="n">
         <v>4.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S57" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V57" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W57" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="X57" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.92</v>
+        <v>3</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['50', '66', '90+5']</t>
+          <t>['22', '52', '59']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45551.66666666666</v>
@@ -7857,35 +7857,35 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Boavista FC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G58" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="O58" t="n">
-        <v>2.63</v>
+        <v>1.99</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="R58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X58" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['14', '22', '75', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI58" t="n">
         <v>1.5</v>
       </c>
-      <c r="S58" t="n">
+      <c r="AJ58" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X58" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['34', '68']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>['23', '45+5']</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45551.67708333334</v>
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,22 +8022,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.57</v>
+        <v>4.92</v>
       </c>
       <c r="M59" t="n">
-        <v>4.45</v>
+        <v>4.72</v>
       </c>
       <c r="N59" t="n">
-        <v>4.24</v>
+        <v>1.47</v>
       </c>
       <c r="O59" t="n">
-        <v>1.99</v>
+        <v>5.24</v>
       </c>
       <c r="P59" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.56</v>
+        <v>1.89</v>
       </c>
       <c r="R59" t="n">
         <v>1.18</v>
@@ -8046,59 +8046,59 @@
         <v>4.33</v>
       </c>
       <c r="T59" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U59" t="n">
         <v>1.85</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.96</v>
       </c>
       <c r="V59" t="n">
         <v>1.01</v>
       </c>
       <c r="W59" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X59" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.14</v>
+        <v>2.72</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['14', '22', '75', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['4', '13', '33', '63', '66', '82']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.33</v>
+        <v>1.16</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AJ59" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45551.67708333334</v>
@@ -8115,35 +8115,35 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Boavista FC</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.92</v>
+        <v>1.94</v>
       </c>
       <c r="M60" t="n">
-        <v>4.72</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
+        <v>4</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W60" t="n">
         <v>1.47</v>
       </c>
-      <c r="O60" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S60" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.09</v>
-      </c>
       <c r="X60" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="Z60" t="n">
-        <v>3.04</v>
+        <v>1.62</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.76</v>
+        <v>4.75</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AD60" t="n">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '68']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['4', '13', '33', '63', '66', '82']</t>
+          <t>['23', '45+5']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>2.63</v>
+        <v>1.28</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="AI60" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45551.67708333334</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,22 +8899,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guaraní</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="M66" t="n">
         <v>3</v>
       </c>
       <c r="N66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O66" t="n">
         <v>3.1</v>
       </c>
-      <c r="O66" t="n">
-        <v>3</v>
-      </c>
       <c r="P66" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q66" t="n">
         <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="S66" t="n">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="T66" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="U66" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V66" t="n">
         <v>1.08</v>
       </c>
       <c r="W66" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="X66" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Z66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH66" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA66" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AI66" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ66" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45551.875</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,22 +9028,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Guaraní</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -9054,65 +9054,65 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O67" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P67" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q67" t="n">
         <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S67" t="n">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="T67" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="U67" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V67" t="n">
         <v>1.08</v>
       </c>
       <c r="W67" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="X67" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA67" t="n">
-        <v>5.2</v>
+        <v>3.86</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -9121,16 +9121,16 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ67" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45551.875</v>
